--- a/astro-site/public/dl/burger-joint-checklist-templates/BONUS-02-burger-joint-holiday-calendar.xlsx
+++ b/astro-site/public/dl/burger-joint-checklist-templates/BONUS-02-burger-joint-holiday-calendar.xlsx
@@ -639,7 +639,7 @@
     <row r="8" ht="31" customHeight="1">
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>▸ Add the dates that matter in your area (local holidays, fairs). UK note: Mothering Sunday (March), bank holidays and Boxing Day, in the free rows</t>
+          <t>▸ Add the dates that matter in your area (local holidays, fairs). UK note: Mothering Sunday (March), National Burger Day (last Thursday in August), bank holidays and Boxing Day, in the free rows</t>
         </is>
       </c>
     </row>
